--- a/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 7,59</t>
+          <t>-3,3; 7,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 2,63</t>
+          <t>-9,26; 3,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -1,84</t>
+          <t>-14,08; -1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 0,85</t>
+          <t>-18,18; 0,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 347,06</t>
+          <t>-52,81; 356,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 100,42</t>
+          <t>-82,71; 94,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,38</t>
+          <t>-100,0; 18,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,47</t>
+          <t>-100,0; 56,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,9</t>
+          <t>-4,35; 0,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,34</t>
+          <t>-3,81; 1,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,71</t>
+          <t>-3,11; 1,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,16</t>
+          <t>-5,44; 0,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 15,78</t>
+          <t>-50,03; 14,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 30,81</t>
+          <t>-52,5; 25,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 38,58</t>
+          <t>-46,07; 39,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 21,02</t>
+          <t>-54,27; 16,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,62</t>
+          <t>-5,12; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,96</t>
+          <t>-4,66; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,38</t>
+          <t>-1,47; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,97</t>
+          <t>-8,14; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 94,79</t>
+          <t>-57,6; 89,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 97,22</t>
+          <t>-65,02; 98,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 356,93</t>
+          <t>-41,64; 362,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 23,18</t>
+          <t>-74,21; 25,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,09</t>
+          <t>-3,27; 0,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,59</t>
+          <t>-3,49; 0,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,31</t>
+          <t>-2,5; 1,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,4</t>
+          <t>-5,3; -0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 18,55</t>
+          <t>-38,65; 18,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 11,24</t>
+          <t>-47,92; 10,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 31,24</t>
+          <t>-40,26; 27,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -5,57</t>
+          <t>-54,3; -4,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,83</t>
+          <t>-3,66; 7,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 3,3</t>
+          <t>-9,48; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -1,98</t>
+          <t>-14,25; -2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 0,84</t>
+          <t>-18,05; 1,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 356,88</t>
+          <t>-49,52; 313,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,71; 94,75</t>
+          <t>-87,99; 84,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,88</t>
+          <t>-100,0; 28,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,6</t>
+          <t>-100,0; 67,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,85</t>
+          <t>-4,58; 0,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,2</t>
+          <t>-3,85; 1,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,71</t>
+          <t>-3,3; 1,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,95</t>
+          <t>-5,07; 1,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 14,41</t>
+          <t>-50,78; 17,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 25,52</t>
+          <t>-51,94; 23,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 39,29</t>
+          <t>-45,13; 44,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 16,58</t>
+          <t>-53,33; 15,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 3,8</t>
+          <t>-4,69; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,89</t>
+          <t>-5,27; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,9</t>
+          <t>-1,6; 5,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 1,29</t>
+          <t>-8,96; 1,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 89,52</t>
+          <t>-52,95; 104,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 98,62</t>
+          <t>-70,85; 85,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 362,1</t>
+          <t>-47,66; 275,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,21; 25,64</t>
+          <t>-75,9; 26,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,95</t>
+          <t>-3,29; 1,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,51</t>
+          <t>-3,25; 0,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,2</t>
+          <t>-2,52; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,32</t>
+          <t>-5,56; -0,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 18,22</t>
+          <t>-39,94; 18,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 10,05</t>
+          <t>-46,28; 8,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 27,79</t>
+          <t>-40,02; 34,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -4,3</t>
+          <t>-54,61; -2,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,37</t>
+          <t>-6,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-65,07%</t>
+          <t>-57,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 7,18</t>
+          <t>-4,02; 7,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 2,74</t>
+          <t>-9,57; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -2,07</t>
+          <t>-14,17; -1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 1,1</t>
+          <t>-17,93; 2,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 313,35</t>
+          <t>-59,41; 347,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,99; 84,42</t>
+          <t>-79,94; 100,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,75</t>
+          <t>-100,0; 20,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,4</t>
+          <t>-100,0; 66,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-25,69%</t>
+          <t>-18,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,92</t>
+          <t>-4,35; 0,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,04</t>
+          <t>-3,63; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,75</t>
+          <t>-3,16; 1,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,05</t>
+          <t>-4,52; 1,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 17,02</t>
+          <t>-49,98; 15,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 23,17</t>
+          <t>-49,64; 30,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 44,03</t>
+          <t>-46,94; 38,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 15,82</t>
+          <t>-45,46; 30,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-3,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-37,91%</t>
+          <t>-37,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,0</t>
+          <t>-4,92; 3,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,68</t>
+          <t>-4,85; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,07</t>
+          <t>-1,81; 5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 1,21</t>
+          <t>-9,5; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 104,33</t>
+          <t>-53,2; 94,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 85,74</t>
+          <t>-65,95; 97,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 275,74</t>
+          <t>-44,48; 356,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 26,37</t>
+          <t>-75,8; 22,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-32,94%</t>
+          <t>-27,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,02</t>
+          <t>-3,11; 1,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,45</t>
+          <t>-3,35; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,37</t>
+          <t>-2,58; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -0,27</t>
+          <t>-5,06; 0,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 18,29</t>
+          <t>-38,87; 18,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 8,73</t>
+          <t>-48,7; 11,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 34,68</t>
+          <t>-42,83; 31,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,61; -2,66</t>
+          <t>-50,63; 2,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-36,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-86,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-57,37%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.995748115116764</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.779383285731535</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-7.26388332253371</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.55054625564126</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3968535397228352</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3676458238839139</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.8665533898351516</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5736713392277653</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,02; 7,59</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; 2,63</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,17; -1,84</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,93; 2,08</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-59,41; 347,06</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-79,94; 100,42</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 20,38</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 66,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.018356867381081</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.568225860422558</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.1653531472539</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.92849713068336</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5941418145818133</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7994460768125069</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.590426212113647</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.631483035130584</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.840343637116085</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.081041291209665</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.470563826140316</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.004239660929031</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2037798788042584</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.6661944312850362</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-23,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-21,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-18,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,35; 0,9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 1,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,16; 1,71</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 1,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-49,98; 15,78</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-49,64; 30,81</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-46,94; 38,58</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-45,46; 30,84</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.735691081012877</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.323944399838386</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.5957932314854197</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.450177078627504</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2350516310677428</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2159130856931436</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1075786778728571</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1843725828121899</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-18,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-37,07%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.346599518984664</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.634242914705955</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.161834697500824</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.517694495181888</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4998366654061195</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4964482347120358</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4694408067415762</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4545976438735405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,92; 3,62</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,85; 2,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 5,38</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,5; 1,04</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-53,2; 94,79</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-65,95; 97,22</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-44,48; 356,93</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-75,8; 22,9</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9026285190069147</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.340089261806851</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.705195956029773</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.869717634705833</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1577589411812494</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3081388425621883</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3858214958861347</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3083765802361905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-23,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-11,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-27,28%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.3843412780268584</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9811128737521401</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.621712144584303</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.237514275201482</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05857191902450609</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1837661945057686</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.5259631207126656</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.370720701899628</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,11; 1,09</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,35; 0,59</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 1,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 0,14</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-38,87; 18,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-48,7; 11,24</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-42,83; 31,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-50,63; 2,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.916230315560151</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.848303711834863</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.81492435210023</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.498005995280682</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5320376433036323</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6594832784148128</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4447911637728494</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7579759085716328</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.622080861565578</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.961215021527636</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.383478898147775</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.037814234014187</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9479109234248703</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.9721628890933904</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.56928182247043</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2289703843675223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.9534313439083688</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.410474805128755</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6204013575452534</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.281577974065425</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1377624935299581</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2308676561253185</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1197161939461218</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2728283839197798</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.107833945789282</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.354776862773266</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.576880149412136</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.059289996225467</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3886912706049289</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4870457614607039</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4282743232494939</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5063182399473733</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.090619371798954</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5941704106585036</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.308614819353522</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.1386251483292507</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1855045084299595</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1123626317966506</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3124156392450821</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.02447698432367294</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
